--- a/data/trans_camb/IP17-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 16,76</t>
+          <t>-3,28; 15,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 15,19</t>
+          <t>-4,97; 14,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 14,99</t>
+          <t>-5,29; 13,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 7,53</t>
+          <t>-12,52; 7,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 8,65</t>
+          <t>-11,58; 7,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,5; -1,48</t>
+          <t>-19,66; -1,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 9,28</t>
+          <t>-4,32; 8,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 8,93</t>
+          <t>-5,42; 8,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 3,43</t>
+          <t>-10,3; 3,21</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 110,63</t>
+          <t>-15,56; 98,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 103,23</t>
+          <t>-20,58; 92,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 109,52</t>
+          <t>-23,84; 93,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 35,69</t>
+          <t>-42,18; 35,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 44,91</t>
+          <t>-37,8; 37,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,52; -6,73</t>
+          <t>-63,7; -4,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 50,13</t>
+          <t>-16,97; 48,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 51,05</t>
+          <t>-21,49; 42,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 18,49</t>
+          <t>-39,63; 16,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 10,63</t>
+          <t>-10,31; 11,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -0,47</t>
+          <t>-20,32; -1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,5; -6,08</t>
+          <t>-24,9; -6,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 3,23</t>
+          <t>-15,99; 3,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 6,4</t>
+          <t>-12,22; 7,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 3,48</t>
+          <t>-15,03; 4,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 4,27</t>
+          <t>-10,96; 3,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 0,58</t>
+          <t>-13,47; -0,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -3,62</t>
+          <t>-17,15; -4,04</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 51,9</t>
+          <t>-33,78; 52,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,5; -1,37</t>
+          <t>-62,35; -4,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,98; -27,0</t>
+          <t>-76,77; -31,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,14; 19,82</t>
+          <t>-56,26; 18,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 36,8</t>
+          <t>-43,95; 42,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 19,64</t>
+          <t>-54,86; 28,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 21,49</t>
+          <t>-37,29; 18,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 3,13</t>
+          <t>-46,99; 0,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,22; -17,45</t>
+          <t>-61,48; -17,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 19,04</t>
+          <t>-3,62; 17,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 10,3</t>
+          <t>-10,77; 9,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -0,43</t>
+          <t>-19,16; -1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 11,91</t>
+          <t>-8,75; 10,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 1,3</t>
+          <t>-17,72; 1,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 7,23</t>
+          <t>-14,0; 7,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 11,29</t>
+          <t>-2,74; 11,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 2,77</t>
+          <t>-11,57; 2,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 0,79</t>
+          <t>-14,14; 0,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 180,42</t>
+          <t>-17,58; 159,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 92,51</t>
+          <t>-50,97; 88,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,07; 5,6</t>
+          <t>-87,58; -8,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 76,69</t>
+          <t>-36,06; 69,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,45; 11,72</t>
+          <t>-71,08; 11,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 42,03</t>
+          <t>-56,09; 45,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 72,05</t>
+          <t>-13,04; 76,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,71; 19,41</t>
+          <t>-50,91; 19,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,46; 6,46</t>
+          <t>-63,5; 7,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 9,88</t>
+          <t>-3,58; 9,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 9,52</t>
+          <t>-3,25; 9,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 0,68</t>
+          <t>-12,54; 0,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 7,83</t>
+          <t>-5,6; 8,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 3,72</t>
+          <t>-9,7; 4,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 0,99</t>
+          <t>-12,82; 1,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 7,73</t>
+          <t>-2,51; 6,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,62</t>
+          <t>-4,79; 4,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -0,89</t>
+          <t>-10,35; -1,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 62,01</t>
+          <t>-15,27; 59,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 60,2</t>
+          <t>-14,13; 60,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 2,37</t>
+          <t>-56,1; 5,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 36,75</t>
+          <t>-19,8; 39,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 18,29</t>
+          <t>-35,93; 23,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 5,14</t>
+          <t>-45,08; 6,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 39,57</t>
+          <t>-10,46; 34,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 24,04</t>
+          <t>-20,14; 22,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,71; -4,21</t>
+          <t>-43,04; -4,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 11,09</t>
+          <t>-5,64; 10,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 8,86</t>
+          <t>-8,43; 8,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 6,42</t>
+          <t>-10,77; 5,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 12,48</t>
+          <t>-2,73; 12,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 10,26</t>
+          <t>-4,9; 10,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 9,66</t>
+          <t>-6,46; 9,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 9,24</t>
+          <t>-1,67; 9,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 7,52</t>
+          <t>-3,38; 7,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,6</t>
+          <t>-6,18; 5,54</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 77,94</t>
+          <t>-23,08; 75,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 59,7</t>
+          <t>-34,23; 62,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 45,81</t>
+          <t>-45,81; 39,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 91,14</t>
+          <t>-15,69; 87,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 77,77</t>
+          <t>-23,43; 78,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 71,18</t>
+          <t>-32,71; 70,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 59,79</t>
+          <t>-7,89; 65,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 50,37</t>
+          <t>-17,03; 49,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 37,25</t>
+          <t>-29,16; 35,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 14,61</t>
+          <t>-6,26; 15,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 14,65</t>
+          <t>-5,87; 13,97</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 8,77</t>
+          <t>-9,05; 9,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 8,92</t>
+          <t>-13,47; 9,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 1,34</t>
+          <t>-19,82; 1,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 3,43</t>
+          <t>-19,4; 3,03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 8,91</t>
+          <t>-5,76; 8,62</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 5,08</t>
+          <t>-10,27; 3,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 2,89</t>
+          <t>-12,22; 2,41</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 155,41</t>
+          <t>-36,47; 157,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 146,21</t>
+          <t>-36,52; 145,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,66; 93,92</t>
+          <t>-50,43; 102,21</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 46,28</t>
+          <t>-45,79; 49,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-66,87; 10,21</t>
+          <t>-66,93; 10,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 21,31</t>
+          <t>-64,23; 24,9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 55,87</t>
+          <t>-25,92; 54,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 31,31</t>
+          <t>-44,94; 25,71</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 21,36</t>
+          <t>-54,24; 17,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,87</t>
+          <t>0,5; 7,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,33</t>
+          <t>-2,83; 4,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,71</t>
+          <t>-8,16; -0,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 3,71</t>
+          <t>-3,56; 3,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,77</t>
+          <t>-6,83; 0,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -1,47</t>
+          <t>-8,91; -1,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,57</t>
+          <t>-0,64; 4,48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,64</t>
+          <t>-3,67; 1,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -2,08</t>
+          <t>-7,47; -2,18</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,54; 43,26</t>
+          <t>2,15; 43,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 24,93</t>
+          <t>-13,32; 25,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,0; -4,16</t>
+          <t>-38,35; -3,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 17,48</t>
+          <t>-14,56; 17,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 4,09</t>
+          <t>-27,85; 2,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-34,26; -6,59</t>
+          <t>-35,85; -6,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 23,4</t>
+          <t>-2,78; 22,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 8,35</t>
+          <t>-16,26; 6,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,6; -10,32</t>
+          <t>-33,45; -11,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 15,3</t>
+          <t>-3,59; 15,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 14,6</t>
+          <t>-4,46; 14,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 13,85</t>
+          <t>-4,7; 14,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 7,63</t>
+          <t>-12,25; 9,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 7,94</t>
+          <t>-11,53; 8,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -1,47</t>
+          <t>-20,17; -1,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 8,99</t>
+          <t>-4,88; 9,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 8,17</t>
+          <t>-5,86; 8,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 3,21</t>
+          <t>-9,85; 3,74</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 98,97</t>
+          <t>-17,0; 109,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 92,38</t>
+          <t>-19,76; 99,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 93,05</t>
+          <t>-22,86; 96,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 35,65</t>
+          <t>-40,09; 51,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 37,5</t>
+          <t>-38,51; 42,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,7; -4,96</t>
+          <t>-66,02; -6,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 48,76</t>
+          <t>-19,4; 48,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 42,25</t>
+          <t>-21,89; 44,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 16,88</t>
+          <t>-39,13; 19,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 11,04</t>
+          <t>-10,04; 10,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -1,33</t>
+          <t>-20,12; -0,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,9; -6,78</t>
+          <t>-24,0; -6,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 3,01</t>
+          <t>-16,7; 3,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 7,0</t>
+          <t>-12,46; 6,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 4,68</t>
+          <t>-15,93; 4,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 3,93</t>
+          <t>-10,11; 4,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,47; -0,09</t>
+          <t>-13,38; 0,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,15; -4,04</t>
+          <t>-17,91; -3,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 52,12</t>
+          <t>-31,74; 51,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,35; -4,85</t>
+          <t>-62,74; -2,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,77; -31,23</t>
+          <t>-75,81; -24,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 18,19</t>
+          <t>-56,26; 18,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 42,17</t>
+          <t>-45,14; 39,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 28,66</t>
+          <t>-57,4; 31,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 18,82</t>
+          <t>-35,21; 21,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 0,38</t>
+          <t>-46,52; 3,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,48; -17,95</t>
+          <t>-61,95; -17,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 17,94</t>
+          <t>-3,1; 18,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 9,35</t>
+          <t>-11,47; 10,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -1,69</t>
+          <t>-20,05; -1,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 10,95</t>
+          <t>-8,47; 10,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 1,46</t>
+          <t>-16,77; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 7,28</t>
+          <t>-13,18; 7,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 11,4</t>
+          <t>-2,36; 11,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 2,51</t>
+          <t>-11,97; 1,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 0,82</t>
+          <t>-12,95; 1,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 159,66</t>
+          <t>-14,78; 173,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 88,02</t>
+          <t>-49,15; 96,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,58; -8,62</t>
+          <t>-87,25; 1,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 69,12</t>
+          <t>-34,86; 71,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 11,8</t>
+          <t>-69,41; 7,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 45,79</t>
+          <t>-54,18; 48,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 76,17</t>
+          <t>-9,93; 79,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 19,78</t>
+          <t>-53,25; 10,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 7,19</t>
+          <t>-59,34; 7,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 9,98</t>
+          <t>-3,54; 9,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 9,63</t>
+          <t>-3,27; 9,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 0,83</t>
+          <t>-12,43; 1,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 8,06</t>
+          <t>-5,0; 8,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 4,26</t>
+          <t>-9,36; 3,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 1,37</t>
+          <t>-12,67; 1,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,88</t>
+          <t>-2,33; 6,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,42</t>
+          <t>-4,51; 4,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,35; -1,06</t>
+          <t>-10,5; -1,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 59,42</t>
+          <t>-14,96; 60,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 60,65</t>
+          <t>-13,82; 56,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,1; 5,26</t>
+          <t>-56,99; 6,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 39,16</t>
+          <t>-17,7; 41,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 23,33</t>
+          <t>-33,44; 15,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 6,14</t>
+          <t>-44,75; 5,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 34,69</t>
+          <t>-10,13; 34,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 22,85</t>
+          <t>-18,66; 22,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,04; -4,81</t>
+          <t>-44,13; -5,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 10,91</t>
+          <t>-5,49; 10,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 8,89</t>
+          <t>-7,12; 8,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 5,74</t>
+          <t>-11,24; 5,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 12,44</t>
+          <t>-3,64; 12,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 10,04</t>
+          <t>-4,98; 10,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 9,29</t>
+          <t>-6,71; 9,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 9,71</t>
+          <t>-2,3; 9,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 7,52</t>
+          <t>-3,41; 7,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 5,54</t>
+          <t>-5,65; 5,46</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 75,92</t>
+          <t>-24,7; 70,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 62,04</t>
+          <t>-31,19; 61,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,81; 39,06</t>
+          <t>-45,87; 35,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 87,6</t>
+          <t>-17,86; 93,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 78,34</t>
+          <t>-23,19; 84,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 70,1</t>
+          <t>-31,32; 69,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 65,22</t>
+          <t>-11,56; 63,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 49,34</t>
+          <t>-17,03; 50,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 35,82</t>
+          <t>-28,25; 36,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 15,01</t>
+          <t>-6,39; 14,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 13,97</t>
+          <t>-5,74; 14,72</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 9,69</t>
+          <t>-9,48; 9,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 9,22</t>
+          <t>-14,03; 9,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 1,45</t>
+          <t>-21,05; 1,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 3,03</t>
+          <t>-19,47; 2,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 8,62</t>
+          <t>-6,45; 9,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,94</t>
+          <t>-10,79; 4,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 2,41</t>
+          <t>-12,4; 2,94</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 157,55</t>
+          <t>-37,98; 160,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 145,22</t>
+          <t>-34,65; 170,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 102,21</t>
+          <t>-51,64; 115,49</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 49,76</t>
+          <t>-46,65; 45,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 10,61</t>
+          <t>-67,49; 10,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 24,9</t>
+          <t>-64,75; 16,37</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 54,85</t>
+          <t>-28,6; 58,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 25,71</t>
+          <t>-47,23; 27,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 17,41</t>
+          <t>-52,37; 21,75</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,5; 7,64</t>
+          <t>0,12; 7,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 4,42</t>
+          <t>-3,07; 4,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -0,58</t>
+          <t>-8,43; -1,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,74</t>
+          <t>-2,95; 3,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 0,44</t>
+          <t>-6,48; 0,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,91; -1,27</t>
+          <t>-8,83; -1,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,48</t>
+          <t>-0,63; 4,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,32</t>
+          <t>-3,97; 1,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -2,18</t>
+          <t>-6,95; -2,02</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2,15; 43,73</t>
+          <t>0,51; 40,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 25,67</t>
+          <t>-14,23; 22,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,35; -3,18</t>
+          <t>-39,71; -5,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 17,93</t>
+          <t>-12,69; 19,02</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 2,17</t>
+          <t>-27,01; 3,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -6,14</t>
+          <t>-35,84; -6,73</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 22,37</t>
+          <t>-2,81; 23,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 6,6</t>
+          <t>-17,38; 6,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -11,06</t>
+          <t>-31,36; -9,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-9,98</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-10,41</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,34</t>
+          <t>-4,1</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 15,81</t>
+          <t>-12,05; 7,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 14,35</t>
+          <t>-11,19; 8,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 14,54</t>
+          <t>-19,11; -0,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 9,28</t>
+          <t>-3,24; 16,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 8,67</t>
+          <t>-4,86; 15,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,17; -1,52</t>
+          <t>-6,77; 11,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 9,37</t>
+          <t>-4,78; 9,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 8,5</t>
+          <t>-4,83; 8,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 3,74</t>
+          <t>-10,57; 2,07</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-7,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-5,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-39,29%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>33,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>24,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-5,35%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-40,96%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-15,11%</t>
+          <t>-18,56%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 109,08</t>
+          <t>-39,0; 35,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 99,67</t>
+          <t>-38,97; 44,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 96,94</t>
+          <t>-62,89; -2,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 51,11</t>
+          <t>-15,04; 110,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 42,89</t>
+          <t>-22,79; 103,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,02; -6,85</t>
+          <t>-29,54; 78,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 48,26</t>
+          <t>-19,68; 50,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 44,67</t>
+          <t>-19,08; 51,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 19,27</t>
+          <t>-41,91; 11,27</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-6,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,62</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-10,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-15,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,69</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,94</t>
+          <t>-15,69</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,56</t>
+          <t>-10,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 10,61</t>
+          <t>-15,74; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,12; -0,95</t>
+          <t>-13,13; 6,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,0; -6,19</t>
+          <t>-15,45; 4,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 3,13</t>
+          <t>-11,48; 10,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 6,79</t>
+          <t>-19,91; -0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 4,84</t>
+          <t>-25,15; -6,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 4,22</t>
+          <t>-10,53; 4,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 0,61</t>
+          <t>-13,23; 0,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,91; -3,88</t>
+          <t>-17,69; -3,88</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-26,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-11,76%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-24,56%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-39,73%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-57,82%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-26,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-11,76%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,95%</t>
+          <t>-59,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-42,96%</t>
+          <t>-43,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 51,0</t>
+          <t>-56,14; 19,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,74; -2,63</t>
+          <t>-45,46; 36,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,81; -24,52</t>
+          <t>-55,44; 23,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 18,01</t>
+          <t>-35,97; 51,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 39,43</t>
+          <t>-61,5; -1,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 31,14</t>
+          <t>-78,35; -31,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 21,46</t>
+          <t>-36,88; 21,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 3,29</t>
+          <t>-46,53; 3,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,95; -17,59</t>
+          <t>-62,77; -18,19</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-7,94</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,86</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,85</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,75</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-10,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,94</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,05</t>
+          <t>-10,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>-6,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 18,55</t>
+          <t>-8,71; 11,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 10,22</t>
+          <t>-16,18; 1,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -1,31</t>
+          <t>-13,52; 7,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 10,93</t>
+          <t>-2,92; 19,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 0,72</t>
+          <t>-11,06; 10,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 7,91</t>
+          <t>-19,45; -1,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 11,95</t>
+          <t>-2,53; 11,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 1,57</t>
+          <t>-11,09; 2,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 1,33</t>
+          <t>-13,7; 0,05</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-39,38%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-14,2%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>46,85%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-4,45%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-60,72%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-39,38%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-15,14%</t>
+          <t>-64,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,04%</t>
+          <t>-37,15%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 173,75</t>
+          <t>-34,54; 76,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 96,64</t>
+          <t>-67,45; 11,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,25; 1,19</t>
+          <t>-52,9; 46,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 71,05</t>
+          <t>-13,97; 180,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,41; 7,07</t>
+          <t>-51,65; 92,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 48,47</t>
+          <t>-87,67; -4,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 79,72</t>
+          <t>-11,14; 72,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,25; 10,92</t>
+          <t>-50,71; 19,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,34; 7,44</t>
+          <t>-64,37; 1,29</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,35</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,03</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,78</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,23</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,4</t>
+          <t>-3,26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,6</t>
+          <t>-4,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 9,78</t>
+          <t>-5,91; 7,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 9,13</t>
+          <t>-9,96; 3,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 1,13</t>
+          <t>-12,31; 0,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 8,47</t>
+          <t>-3,05; 9,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 3,09</t>
+          <t>-2,82; 9,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 1,19</t>
+          <t>-9,78; 3,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 6,97</t>
+          <t>-2,39; 7,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,54</t>
+          <t>-4,64; 4,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -1,05</t>
+          <t>-8,62; 0,37</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-13,32%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-22,06%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>15,94%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>15,42%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-29,45%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-13,32%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-22,27%</t>
+          <t>-16,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,51%</t>
+          <t>-19,3%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 60,79</t>
+          <t>-21,39; 36,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 56,11</t>
+          <t>-35,73; 18,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 6,81</t>
+          <t>-44,26; 5,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 41,13</t>
+          <t>-13,83; 62,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 15,5</t>
+          <t>-11,95; 60,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 5,66</t>
+          <t>-43,21; 20,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 34,74</t>
+          <t>-9,26; 39,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 22,95</t>
+          <t>-18,94; 24,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,13; -5,08</t>
+          <t>-35,19; 2,21</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,61</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,02</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,69</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,99</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,69</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,02</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>-2,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 10,85</t>
+          <t>-2,74; 12,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 8,95</t>
+          <t>-4,41; 10,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 5,42</t>
+          <t>-5,27; 9,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 12,32</t>
+          <t>-5,75; 11,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 10,93</t>
+          <t>-7,64; 8,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 9,24</t>
+          <t>-11,01; 5,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 9,66</t>
+          <t>-2,61; 9,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 7,59</t>
+          <t>-4,16; 7,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 5,46</t>
+          <t>-6,11; 5,59</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17,95%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>15,48%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3,56%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-11,5%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>-13,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-0,6%</t>
+          <t>-1,2%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 70,51</t>
+          <t>-14,02; 91,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 61,64</t>
+          <t>-21,59; 77,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 35,04</t>
+          <t>-27,13; 72,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 93,32</t>
+          <t>-24,12; 77,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 84,63</t>
+          <t>-32,72; 59,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 69,52</t>
+          <t>-47,07; 42,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 63,43</t>
+          <t>-12,47; 59,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 50,72</t>
+          <t>-19,73; 50,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 36,62</t>
+          <t>-29,33; 35,54</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,51</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-9,79</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-9,88</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>3,94</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>4,08</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-2,51</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-9,79</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-9,04</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,56</t>
+          <t>-5,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 14,98</t>
+          <t>-14,36; 8,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 14,72</t>
+          <t>-20,22; 1,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 9,36</t>
+          <t>-20,37; 2,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 9,02</t>
+          <t>-6,63; 14,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 1,6</t>
+          <t>-7,05; 14,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 2,62</t>
+          <t>-10,53; 9,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 9,03</t>
+          <t>-6,66; 8,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 4,43</t>
+          <t>-10,16; 5,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 2,94</t>
+          <t>-12,49; 2,2</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-9,95%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-38,79%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-39,15%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>28,33%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>29,35%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-2,38%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-9,95%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-38,79%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-35,8%</t>
+          <t>-2,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-23,4%</t>
+          <t>-25,68%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 160,12</t>
+          <t>-47,0; 46,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 170,62</t>
+          <t>-66,87; 10,21</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 115,49</t>
+          <t>-66,9; 17,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-46,65; 45,82</t>
+          <t>-38,75; 155,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 10,1</t>
+          <t>-39,37; 146,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,75; 16,37</t>
+          <t>-54,34; 95,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 58,82</t>
+          <t>-28,89; 55,87</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 27,13</t>
+          <t>-43,97; 31,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,37; 21,75</t>
+          <t>-53,52; 14,46</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2,77</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-4,87</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,97</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,72</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,41</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-2,77</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,97</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,67</t>
+          <t>-4,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,26</t>
+          <t>-3,39; 3,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,02</t>
+          <t>-6,2; 0,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -1,06</t>
+          <t>-8,13; -1,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,85</t>
+          <t>0,42; 7,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,63</t>
+          <t>-2,62; 4,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -1,41</t>
+          <t>-7,71; -0,86</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,71</t>
+          <t>-0,49; 4,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,21</t>
+          <t>-3,69; 1,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -2,02</t>
+          <t>-7,21; -1,93</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-12,39%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-21,79%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>20,45%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-22,71%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-12,39%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-22,23%</t>
+          <t>-22,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-22,27%</t>
+          <t>-21,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0,51; 40,12</t>
+          <t>-14,44; 17,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 22,95</t>
+          <t>-25,12; 4,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,71; -5,63</t>
+          <t>-34,03; -5,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 19,02</t>
+          <t>1,54; 43,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 3,09</t>
+          <t>-12,71; 24,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -6,73</t>
+          <t>-37,25; -5,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 23,79</t>
+          <t>-2,28; 23,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 6,36</t>
+          <t>-16,62; 8,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-31,36; -9,92</t>
+          <t>-32,32; -10,07</t>
         </is>
       </c>
     </row>
